--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,17 +1910,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Telnet 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1983,6 +1983,104 @@
         </is>
       </c>
       <c r="S14" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Telnet 弱密码</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:54</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>192.168.30.190</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -1993,98 +2091,6 @@
 [Yes]</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LDAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2202,17 +2208,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IMAP 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abc123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2274,13 +2280,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2292,6 +2292,98 @@
         </is>
       </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sangfor@123</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EDR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-17 21:02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:02</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10.74.107.111</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>未暴露</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>内网</t>
         </is>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -1033,17 +1033,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LDAP 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1101,7 +1101,13 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1121,17 +1127,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMAP 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abc123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1189,13 +1195,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>未加白</t>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,38 +541,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SNMP 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>admin123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-23 16:16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-23 16:16</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MSS研发组</t>
+          <t>test22222</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -597,7 +597,11 @@
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>22</t>
@@ -629,42 +633,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WEB弱密码</t>
+          <t>FTP 弱密码</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>baoxy18</t>
+          <t>ftp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>cskm.midea.com/kbs/sso/train-qrcode</t>
-        </is>
-      </c>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜-服务版</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-08 13:50</t>
+          <t>2026-06-23 16:09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-08 13:17</t>
+          <t>2026-06-23 16:09</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>192.168.26.44</t>
+          <t>10.128.160.50</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MSS研发组</t>
+          <t>test22222</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -689,10 +689,14 @@
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -701,33 +705,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>页面url: cskm.midea.com/kbs/sso/train-qrcode
-请求体: POST /kbs/sso/train-qrcode HTTP/1.1
-Host: cskm.midea.com
-Origin: http://cskm.midea.com
-Content-Type: application/x-www-form-urlencoded; charset=UTF-8
-Accept-Language: zh-CN,zh-Hans;q=0.9
-Accept-Encoding: gzip, deflate
-Connection: keep-alive
-Accept: application/json, text/javascript, */*; q=0.01
-User-Agent: Mozilla/5.0 (iPhone; CPU iPhone OS 17_3_1 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148 MicroMessenger/8.0.47(0x18002f2a) NetType/4G Language/zh_CN
-Referer: http://cskm.midea.com/static/wing/qrcode/qrcode.html?trainQrCodeId=1afb73a3-b126-4f48-a504-8971055f8e37
-Content-Length: 84
-X-Requested-With: XMLHttpRequest
-loginName=baoxy18&amp;password=123456&amp;trainQrCodeId=1afb73a3-b126-4f48-a504-8971055f8e37
-响应体: HTTP/1.1 200 OK
-Server: openresty/1.21.4.1
-Date: Fri, 01 Mar 2024 01:52:36 GMT
-Content-Type: application/json;charset=UTF-8
-Content-Length: 176
-Connection: keep-alive
-Set-Cookie: JSESSIONID=7B8A48F49600D2FE4B51B5029A049E60; Path=/kbs/; HttpOnly
-Accept-Charset: big5, big5-hkscs, cesu-8, euc-jp, euc-kr, gb18030, gb2312, gbk, ibm-thai, ibm00858, ibm01140, ibm01141, ibm01142, ibm01143, ibm01144, ibm01145, ibm01146, ibm01147, ibm01148, ibm01149, ibm037, ibm1026, ibm1047, ibm273, ibm277, ibm278, ibm280, ibm284, ibm285, ibm290, ibm297, ibm420, ibm424, ibm437, ibm500, ibm775, ibm850, ibm852, ibm855, ibm857, ibm860, ibm861, ibm862, ibm863, ibm864, ibm865, ibm866, ibm868, ibm869, ibm870, ibm871, ibm918, iso-2022-cn, iso-2022-jp, iso-2022-jp-2, iso-2022-kr, iso-8859-1, iso-8859-13, iso-8859-15, iso-8859-2, iso-8859-3, iso-8859-4, iso-8859-5, iso-8859-6, iso-8859-7, iso-8859-8, iso-8859-9, jis_x0201, jis_x0212-1990, koi8-r, koi8-u, shift_jis, tis-620, us-ascii, utf-16, utf-16be, utf-16le, utf-32, utf-32be, utf-32le, utf-8, windows-1250, windows-1251, windows-1252, windows-1253, windows-1254, windows-1255, windows-1256, windows-1257, windows-1258, windows-31j, x-big5-hkscs-2001, x-big5-solaris, x-compound_text, x-euc-jp-linux, x-euc-tw, x-eucjp-open, x-ibm1006, x-ibm1025, x-ibm1046, x-ibm1097, x-ibm1098, x-ibm1112, x-ibm1122, x-ibm1123, x-ibm1124, x-ibm1166, x-ibm1364, x-ibm1381, x-ibm1383, x-ibm300, x-ibm33722, x-ibm737, x-ibm833, x-ibm834, x-ibm856, x-ibm874, x-ibm875, x-ibm921, x-ibm922, x-ibm930, x-ibm933, x-ibm935, x-ibm937, x-ibm939, x-ibm942, x-ibm942c, x-ibm943, x-ibm943c, x-ibm948, x-ibm949, x-ibm949c, x-ibm950, x-ibm964, x-ibm970, x-iscii91, x-iso-2022-cn-cns, x-iso-2022-cn-gb, x-iso-8859-11, x-jis0208, x-jisautodetect, x-johab, x-macarabic, x-maccentraleurope, x-maccroatian, x-maccyrillic, x-macdingbat, x-macgreek, x-machebrew, x-maciceland, x-macroman, x-macromania, x-macsymbol, x-macthai, x-macturkish, x-macukraine, x-ms932_0213, x-ms950-hkscs, x-ms950-hkscs-xp, x-mswin-936, x-pck, x-sjis_0213, x-utf-16le-bom, x-utf-32be-bom, x-utf-32le-bom, x-windows-50220, x-windows-50221, x-windows-874, x-windows-949, x-windows-950, x-windows-iso2022jp
-{"code":"000012","message":"baoxy18登录成功","data":{"trainId":"31f0ad2b-5090-4a3a-b1db-cf29146fd646","loginName":"baoxy18","token":"dd21166a-ba62-4972-9358-b16b4f5ed1fe"}}</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -747,17 +725,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Telnet 弱密码</t>
+          <t>FTP 弱密码</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>sangfor@123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>sangfor@123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -768,27 +746,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-21 18:08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-21 18:08</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>192.168.101.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MSS研发组</t>
+          <t>test22222</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -803,10 +781,14 @@
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -816,6 +798,784 @@
         </is>
       </c>
       <c r="S4" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 230, "reply_msg": "user logged in."}</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IMAP 弱密码</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xjj_ser@sip.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:45</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>192.168.107.1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": "OK", "reply_msg": "LOGIN OK."}</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>POP3 弱密码</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sipt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sipt</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-21 10:21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-21 10:21</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>192.168.102.1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": "+OK", "reply_msg": "sipt user logged in"}</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SNMP 弱密码</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POP3 弱密码</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IMAP 弱密码</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abc123</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Telnet 弱密码</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -826,569 +1586,109 @@
 [Yes]</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>POP3 弱密码</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LDAP 弱密码</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>FTP 弱密码</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IMAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LDAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SMTP 弱密码</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>abcd123</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-06-16 13:54</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>192.168.30.190</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RDP 弱密码</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sangfor@123</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>EDR</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-03-16 21:02</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>10.74.107.111</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>服务器</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3389</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>未暴露</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>内网</t>
         </is>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,48 +541,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>xjj_ser@sip.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>admin123</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>云镜-服务版</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:16</t>
+          <t>2026-06-26 22:55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:16</t>
+          <t>2025-09-22 16:28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.128.160.50</t>
+          <t>200.200.221.86</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>test22222</t>
+          <t>未归类组</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -604,7 +604,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -613,7 +613,13 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {}</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -633,38 +639,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ftp</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ftp</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>云镜-服务版</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:09</t>
+          <t>2026-06-26 16:47</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:09</t>
+          <t>2026-06-26 16:47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10.128.160.50</t>
+          <t>10.65.196.170</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>test22222</t>
+          <t>未归类组</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -696,7 +702,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -725,17 +731,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>SNMP 弱密码</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sangfor@123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sangfor@123</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -746,17 +752,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-21 18:08</t>
+          <t>2026-06-26 16:37</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-21 18:08</t>
+          <t>2026-06-26 16:37</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>192.168.101.1</t>
+          <t>1.1.1.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -766,11 +772,15 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>test22222</t>
+          <t>未归类组</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>普通资产</t>
@@ -788,7 +798,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -797,785 +807,1515 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WinRM 弱密码</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:26</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10.128.165.28</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10.128.165.25</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSH 弱密码</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:20</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.128.165.150</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:18</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10.128.165.26</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:16</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.128.165.52</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>未归类组</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSH 弱密码</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>admin123</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:16</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>云镜-服务版</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:09</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10.128.160.50</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sangfor@123</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sangfor@123</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-21 18:08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-06-21 18:08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>192.168.101.1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": 230, "reply_msg": "user logged in."}</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>IMAP 弱密码</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>xjj_ser@sip.com</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-06-21 11:45</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-06-21 11:45</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>192.168.107.1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>服务器</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": "OK", "reply_msg": "LOGIN OK."}</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>POP3 弱密码</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>sipt</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>sipt</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-06-21 10:21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-06-21 10:21</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>192.168.102.1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>服务器</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": "+OK", "reply_msg": "sipt user logged in"}</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SNMP 弱密码</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>192.168.50.190</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>终端</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FTP 弱密码</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SMTP 弱密码</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>abcd123</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>POP3 弱密码</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>192.168.50.190</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>终端</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>POP3 弱密码</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IMAP 弱密码</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>abc123</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>192.168.50.190</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>终端</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IMAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
 响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LDAP 弱密码</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SNMP 弱密码</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Telnet 弱密码</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>192.168.50.190</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>终端</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -1586,109 +2326,115 @@
 [Yes]</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>内网</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LDAP 弱密码</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>SIP</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-05-31 02:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>192.168.50.190</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>终端</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>test22222</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>445</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>未加白</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>待处置</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>内网</t>
         </is>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -1765,17 +1765,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SMTP 弱密码</t>
+          <t>IMAP 弱密码</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>admin1</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abcd123</t>
+          <t>abc123</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
         <is>
           <t>页面url: -
 请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1863,12 +1863,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POP3 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1935,13 +1935,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1961,17 +1955,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IMAP 弱密码</t>
+          <t>SNMP 弱密码</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abc123</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2024,7 +2018,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -2033,13 +2027,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2059,12 +2047,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LDAP 弱密码</t>
+          <t>Telnet 弱密码</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2131,191 +2119,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SNMP 弱密码</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Telnet 弱密码</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -2326,6 +2130,202 @@
 [Yes]</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2345,7 +2345,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>POP3 弱密码</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -1863,12 +1863,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LDAP 弱密码</t>
+          <t>Telnet 弱密码</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1935,191 +1935,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SNMP 弱密码</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>未加白</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Telnet 弱密码</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SIP</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-05-31 02:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>192.168.50.190</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>test22222</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>页面url: -
 请求体: -
@@ -2130,6 +1946,202 @@
 [Yes]</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>POP3 弱密码</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SMTP 弱密码</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>admin1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>abcd123</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>192.168.50.190</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>终端</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>test22222</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>页面url: -
+请求体: -
+响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2149,7 +2161,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>SNMP 弱密码</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2159,7 +2171,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2212,7 +2224,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2221,13 +2233,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2247,17 +2253,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SMTP 弱密码</t>
+          <t>LDAP 弱密码</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>admin1</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abcd123</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2319,13 +2325,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -2345,7 +2345,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>POP3 弱密码</t>
+          <t>FTP 弱密码</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -541,38 +541,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SNMP 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 18:05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-25 18:05</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.150</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,47 +633,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WEB弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>baoxy18</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>cskm.midea.com/kbs/sso/train-qrcode</t>
-        </is>
-      </c>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-08 13:50</t>
+          <t>2026-06-28 18:04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-08 13:17</t>
+          <t>2026-06-26 18:04</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>192.168.26.44</t>
+          <t>10.128.165.151</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -681,7 +677,11 @@
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>businessPtwtykb_Dnanw</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>未托管</t>
+          <t>已托管</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -709,33 +709,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>页面url: cskm.midea.com/kbs/sso/train-qrcode
-请求体: POST /kbs/sso/train-qrcode HTTP/1.1
-Host: cskm.midea.com
-Origin: http://cskm.midea.com
-Content-Type: application/x-www-form-urlencoded; charset=UTF-8
-Accept-Language: zh-CN,zh-Hans;q=0.9
-Accept-Encoding: gzip, deflate
-Connection: keep-alive
-Accept: application/json, text/javascript, */*; q=0.01
-User-Agent: Mozilla/5.0 (iPhone; CPU iPhone OS 17_3_1 like Mac OS X) AppleWebKit/605.1.15 (KHTML, like Gecko) Mobile/15E148 MicroMessenger/8.0.47(0x18002f2a) NetType/4G Language/zh_CN
-Referer: http://cskm.midea.com/static/wing/qrcode/qrcode.html?trainQrCodeId=1afb73a3-b126-4f48-a504-8971055f8e37
-Content-Length: 84
-X-Requested-With: XMLHttpRequest
-loginName=baoxy18&amp;password=123456&amp;trainQrCodeId=1afb73a3-b126-4f48-a504-8971055f8e37
-响应体: HTTP/1.1 200 OK
-Server: openresty/1.21.4.1
-Date: Fri, 01 Mar 2024 01:52:36 GMT
-Content-Type: application/json;charset=UTF-8
-Content-Length: 176
-Connection: keep-alive
-Set-Cookie: JSESSIONID=7B8A48F49600D2FE4B51B5029A049E60; Path=/kbs/; HttpOnly
-Accept-Charset: big5, big5-hkscs, cesu-8, euc-jp, euc-kr, gb18030, gb2312, gbk, ibm-thai, ibm00858, ibm01140, ibm01141, ibm01142, ibm01143, ibm01144, ibm01145, ibm01146, ibm01147, ibm01148, ibm01149, ibm037, ibm1026, ibm1047, ibm273, ibm277, ibm278, ibm280, ibm284, ibm285, ibm290, ibm297, ibm420, ibm424, ibm437, ibm500, ibm775, ibm850, ibm852, ibm855, ibm857, ibm860, ibm861, ibm862, ibm863, ibm864, ibm865, ibm866, ibm868, ibm869, ibm870, ibm871, ibm918, iso-2022-cn, iso-2022-jp, iso-2022-jp-2, iso-2022-kr, iso-8859-1, iso-8859-13, iso-8859-15, iso-8859-2, iso-8859-3, iso-8859-4, iso-8859-5, iso-8859-6, iso-8859-7, iso-8859-8, iso-8859-9, jis_x0201, jis_x0212-1990, koi8-r, koi8-u, shift_jis, tis-620, us-ascii, utf-16, utf-16be, utf-16le, utf-32, utf-32be, utf-32le, utf-8, windows-1250, windows-1251, windows-1252, windows-1253, windows-1254, windows-1255, windows-1256, windows-1257, windows-1258, windows-31j, x-big5-hkscs-2001, x-big5-solaris, x-compound_text, x-euc-jp-linux, x-euc-tw, x-eucjp-open, x-ibm1006, x-ibm1025, x-ibm1046, x-ibm1097, x-ibm1098, x-ibm1112, x-ibm1122, x-ibm1123, x-ibm1124, x-ibm1166, x-ibm1364, x-ibm1381, x-ibm1383, x-ibm300, x-ibm33722, x-ibm737, x-ibm833, x-ibm834, x-ibm856, x-ibm874, x-ibm875, x-ibm921, x-ibm922, x-ibm930, x-ibm933, x-ibm935, x-ibm937, x-ibm939, x-ibm942, x-ibm942c, x-ibm943, x-ibm943c, x-ibm948, x-ibm949, x-ibm949c, x-ibm950, x-ibm964, x-ibm970, x-iscii91, x-iso-2022-cn-cns, x-iso-2022-cn-gb, x-iso-8859-11, x-jis0208, x-jisautodetect, x-johab, x-macarabic, x-maccentraleurope, x-maccroatian, x-maccyrillic, x-macdingbat, x-macgreek, x-machebrew, x-maciceland, x-macroman, x-macromania, x-macsymbol, x-macthai, x-macturkish, x-macukraine, x-ms932_0213, x-ms950-hkscs, x-ms950-hkscs-xp, x-mswin-936, x-pck, x-sjis_0213, x-utf-16le-bom, x-utf-32be-bom, x-utf-32le-bom, x-windows-50220, x-windows-50221, x-windows-874, x-windows-949, x-windows-950, x-windows-iso2022jp
-{"code":"000012","message":"baoxy18登录成功","data":{"trainId":"31f0ad2b-5090-4a3a-b1db-cf29146fd646","loginName":"baoxy18","token":"dd21166a-ba62-4972-9358-b16b4f5ed1fe"}}</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -755,38 +729,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LDAP 弱密码</t>
+          <t>RDP 弱密码</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-07-02 18:05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-07-02 18:05</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -796,7 +770,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MSS研发组</t>
+          <t>yj设备组</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -818,7 +792,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -847,38 +821,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMAP 弱密码</t>
+          <t>HTTP_basic弱口令漏洞</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abc123</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://10.128.165.118:80</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 20:24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-25 20:27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.118</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -910,7 +888,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -921,9 +899,222 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": "OK", "reply_msg": "hello"}</t>
+          <t>页面url: http://10.128.165.118:80
+请求体: GET  HTTP/1.1
+Host: 10.128.165.118:80
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Authorization: Basic YWRtaW46YWRtaW4= 
+响应体: HTTP/1.1 200 OK
+Date: Tue, 19 Mar 1996 15:04:10 GMT
+Server: cisco-IOS
+Transfer-Encoding: chunked
+Content-Type: text/html
+Expires: Tue, 19 Mar 1996 15:04:10 GMT
+Last-Modified: Tue, 19 Mar 1996 15:04:10 GMT
+Cache-Control: no-store, no-cache, must-revalidate
+Accept-Ranges: none 
+ &lt;!-- Copyright (c) 2003-2006, 2008 by Cisco Systems, Inc. --&gt;
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.0 Transitional//EN"&gt;
+&lt;html&gt;
+&lt;head&gt;
+&lt;meta http-equiv="pragma" content="no-cache"&gt;
+&lt;LINK rel="stylesheet" href="stylesheet.css" type="text/css"&gt;
+&lt;title&gt;&lt;/title&gt;
+&lt;style&gt;
+.rightTopBorder {
+	border-top:2px inset;
+	border-right:2px inset;
+}
+.leftTopBorder {
+	border-top:2px inset;
+	border-left:2px inset;
+}
+&lt;/style&gt;
+&lt;script language="JavaScript" src="preflight.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="ajax.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="discover.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="framework.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="fpv.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="title.js"&gt;&lt;/script&gt;
+&lt;script&gt;
+top.dataCache.put("LANGUAGE_CODE", "en");
+top.dataCache.put("CHARSET", "Windows-1252");
+var documentURL = document.location.href;
+var userPreference = retrieveCookie("SSLPreference");
+function initCookie(){
+	var cookie = retrieveCookie("gettingstarted");
+	if(cookie == "")
+	{
+		top.showHelp("Getting Started");
+		document.cookie = "gettingstarted=1;expires=" + cookieExpiryDate();
+	}
+}
+function retrieveCookie(_cookieName) {
+	var cookies = document.cookie.split("; ");
+	for (var i=0; i &lt; cookies.length; i++)
+	{
+	var cookieName = cookies[i].split("=");
+	if (_cookieName == cookieName[0]) 
+	  return unescape(cookieName[1]);
+	}
+	return "";
+}
+function cookieExpiryDate() {
+	date = new Date();
+	return (new Date(date.setDate(date.getYear()+10))).toGMTString();
+} 
+if(getcookie("Cisco_DeviceManager")) 
+{}
+	else
+{
+launchPreflight();
+}
+function loadHTTPS(rememberPref, securePort) {
+	var port = "";
+	if(rememberPref)
+		document.cookie = "SSLPreference=2;expires=" + top.cookieExpiryDate();
+	if(securePort != "" &amp;&amp; !isNaN(parseInt(securePort)) &amp;&amp; parseInt(securePort) != 443)
+		port = ":" + securePort;
+	//alert(documentURL.replace(/http:\/\//, "https://").replace(/([0-9]+)\//, "$1") + port);
+	//document.location.href = documentURL.replace(/http:\/\//, "https://").replace(/([0-9]+)\//, "$1") + port;
+	document.location.href = "https://" + document.location.href.split("/")[2].split(":")[0] + port;
+}
+&lt;/script&gt;
+&lt;/head&gt;	 
+&lt;SCRIPT language="JavaScript"&gt;
+      &lt;!--
+	 window.onbeforeunload=notifyBrowserClose;
+	 if(documentURL.indexOf("http://") == 0  &amp;&amp; document.referrer.indexOf("sslhome.shtml") &lt; 0  &amp;&amp; document.referrer.indexOf("redirect.htm") &lt; 0 &amp;&amp; userPreference != 1)
+	  {
+		document.write('&lt;frameset rows="0,*" cols="*" id="sslFrameset" frameborder="no" border="0" framespacing="0"&gt;');
+	  	document.write('&lt;frame src="frmwrkResource.htm" name="resourceFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+		document.write("&lt;frame src='sslhome.shtml' name='mainFrame' scrolling='NO' marginwidth='0' marginheight='0' noresize&gt;&lt;/frame&gt;");
+	  	document.write("&lt;/frameset&gt;");	
+	  }
+	  else
+	  {
+		if(!isOlderNetscape())
+		{
+			window.document.writeln('&lt;frameset rows="0,0,0,72,134,*,1,0,0,0" cols="*" framespacing="0" frameborder="no" border="0"   onload="initCookie()"&gt;');
+			document.write('&lt;frame src="frmwrkResource.htm" name="resourceFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			window.document.writeln('&lt;frame src="discover.shtml" name="discoveryFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			window.document.write(' &lt;frame src="monitordata.shtml" name="healthFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="toolbar.shtml" name="toolbarFrame" scrolling="NO" marginwidth="2" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="topbanner.htm" name="topFrame" scrolling="NO" noresize marginwidth="2" marginheight="0"&gt;');
+			document.write('&lt;frameset cols="185,*" frameborder="yes" border="10" framespacing="10"&gt;');
+			document.write('&lt;frame src="menu.shtml" name="leftFrame" target="mainFrame"&gt;');
+			document.write('&lt;frameset name="contentFrameset" rows="*,40" cols="*" framespacing="0" frameborder="no" border="0" class="leftTopBorder"&gt;');
+			document.write('&lt;frame src="dashboard.shtml" name="mainFrame" marginwidth="2" marginheight="0"&gt;'); 
+			document.write('&lt;frame src="bottombanner.htm" name="bottomFrame" marginwidth="2" marginheight="0" scrolling="NO"&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;frame src="printframe.htm" name="printFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="submitFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="reloadStatus" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="ajaxFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;noframes&gt;&lt;body&gt;');
+			document.write('These pages use Frames. Please make sure that the browser fully supports Frames feature!');
+			document.write('&lt;/body&gt;&lt;/noframes&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;/html&gt;');
+		}
+	 }
+	// --&gt;&lt;/SCRIPT&gt;
+&lt;NOSCRIPT&gt;
+&lt;body bgcolor="#F8F8F8"&gt;
+&lt;TABLE height=63 cellSpacing=0 cellPadding=0 width="100%" bgColor="#F8F8F8"
+  border=0&gt;
+    &lt;!--DWLayoutTable--&gt;
+    &lt;TR&gt; 
+      &lt;TD vAlign=top align="left" rowSpan=2&gt;&lt;IMG height=7 
+      src="/images/spacer.gif" width=7 border=0&gt; &lt;A 
+      href="http://www.cisco.com/"&gt;&lt;IMG alt="Cisco Systems" 
+      src="/images/logo.gif"  border=0&gt;&lt;/A&gt; &lt;/TD&gt;
+     &lt;/TR&gt;
+  &lt;/TABLE&gt;
+&lt;TABLE align="center" bgcolor="#F8F8F8" cellSpacing=0 cellPadding=0 width="75%" border=0&gt;
+    &lt;TBODY&gt;
+	&lt;TR&gt;
+        &lt;TD bgcolor="#F8F8F8" vAlign=bottom align=center width=772 class="contentheader_nogradient"&gt; 
+          Startup Report&lt;/FONT&gt;&lt;/B&gt;&lt;/FONT&gt;&lt;/TD&gt;
+	&lt;/TR&gt;
+    &lt;/TBODY&gt;
+&lt;/TABLE&gt;
+&lt;TABLE  borderColorDark=#ffffff width="75%" align="center" bgColor="#858A91" borderColorLight=#ffffff border="0"  cellpadding="0" cellspacing="1"&gt;
+                      &lt;!--DWLayoutTable--&gt;
+                      &lt;TBODY&gt;
+                        &lt;TR&gt; 
+                          &lt;TD width=124 height=109 vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff 
+    bgColor=#ffffff&gt; 
+ &lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;A 
+      href="en/troubleshooting_JavaScript.htm"&gt; &lt;IMG height=32 
+      src="images/fatal_error_big.gif" width=32 border=0&gt; &lt;/A&gt; &lt;/NOSCRIPT&gt; &lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD width="152" align="center" vAlign=center bgcolor="#FFFFFF"&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;JavaScript&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD width="704" align="center" vAlign="middle" bgcolor="#FFFFFF"  &gt; 
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt; 
+                            &lt;NOSCRIPT&gt;
+                            JavaScript has not been enabled.&lt;br&gt; The device manger 
+                            will not launch until JavaScript is enabled.&lt;br&gt; Click 
+                            &lt;A 
+      href="en/troubleshooting_JavaScript.htm"&gt;here&lt;/A&gt;&amp;nbsp; for&amp;nbsp; more information.&lt;FONT 
+      color=#800000&gt;&amp;nbsp;&amp;nbsp;&lt;/FONT&gt; 
+                            &lt;/NOSCRIPT&gt;
+                            &lt;/FONT&gt;&lt;/P&gt;&lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;TR&gt; 
+                          &lt;TD height=109 vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff 
+    bgColor=#ffffff&gt; 
+		&lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;IMG height=32 
+      src="images/question.gif" width=32 border=0&gt; &lt;/NOSCRIPT&gt; &lt;b&gt;&lt;font color="#012d32" size="2" face="Arial"&gt; 
+                            &lt;/font&gt;&lt;/b&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD nowrap align=left vAlign=center bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;Internet 
+                              Browser&amp;nbsp;&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD align="center" vAlign="middle"   bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt; 
+                            &lt;NOSCRIPT&gt;
+                            The Internet browser status is unknown. Click&lt;FONT 
+      color=#012d32&gt; &lt;/FONT&gt;&lt;A 
+      href="en/troubleshooting_Browser.htm"&gt;&lt;FONT 
+      color=#013741&gt;here&lt;/FONT&gt;&lt;/A&gt; for more information.&amp;nbsp; 
+                            &lt;/NOSCRIPT&gt;
+                            &lt;/FONT&gt;&lt;/P&gt;&lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;TR&gt; 
+                          &lt;TD height=109 align=left vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff bgColor=#ffffff&gt;&lt;FONT 
+      face=Arial size=2&gt;  
+		&lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt; &lt;IMG height=32 
+      src="images/question.gif" width=32 border=0&gt; &lt;/NOSCRIPT&gt; &lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD nowrap align="center" vAlign="middle" bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;Operating 
+                              System&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD class="homecontent" align="center" vAlign="middle" bgColor=#ffffff&gt; 
+                             &lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt;The operating 
+                              system status is unknown. Click&lt;FONT color=#012d32&gt; 
+                              &lt;/FONT&gt;&lt;A 
+      href="en/troubleshooting_OS.htm"&gt;&lt;FONT 
+      color=#013741&gt;here&lt;/FONT&gt;&lt;/A&gt; for more information.&amp;nbsp; &lt;/FONT&gt; 
+                            &lt;/NOSCRIPT&gt;&lt;/P&gt;
+                            &lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;tr&gt; 
+						  &lt;TD colspan="3" align="right" valign="bottom" bgcolor="#FFFFFF"&gt; &lt;FONT 
+           class="homecontent"&gt; Copyright (c) 2003-2006, 2008 by Cisco Systems, Inc. &lt;/FONT&gt; &lt;/td&gt; 
+                        &lt;/tr&gt;   
+                      &lt;/TBODY&gt;
+                    &lt;/TABLE&gt;
+&lt;/body&gt;
+&lt;html&gt;
+&lt;/NOSCRIPT&gt;
+举证描述: 10.128.165.118资产80端口开启了HTTP auth服务，存在弱密码。用户名:admin，密码:admin</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -945,7 +1136,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FTP 弱密码</t>
+          <t>WinRM 弱密码</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -955,28 +1146,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 18:05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-25 18:06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1008,7 +1199,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1017,13 +1208,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1043,38 +1228,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SMTP 弱密码</t>
+          <t>RDP 弱密码</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>admin1</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abcd123</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 18:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-26 18:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.100</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1106,7 +1291,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1115,13 +1300,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1141,38 +1320,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POP3 弱密码</t>
+          <t>RDP 弱密码</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 18:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-25 18:04</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1204,7 +1383,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1213,13 +1392,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: {"reply_code": 1, "reply_msg": "hello"}</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1239,38 +1412,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Telnet 弱密码</t>
+          <t>RDP 弱密码</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SIP</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-28 18:04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-16 13:54</t>
+          <t>2026-06-25 18:04</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>192.168.30.190</t>
+          <t>10.128.165.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1302,7 +1475,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1311,17 +1484,7 @@
           <t>未知</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>页面url: -
-请求体: -
-响应体: *===============================================================
-Microsoft Telnet Server.
-*===============================================================
-C:\Users\Administrator.pc-PC&gt;
-[Yes]</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>未加白</t>
@@ -1351,28 +1514,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sangfor@123</t>
+          <t>Admin123</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EDR</t>
+          <t>云镜</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-17 21:02</t>
+          <t>2026-06-28 18:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-03-16 21:02</t>
+          <t>2026-06-25 18:04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.74.107.111</t>
+          <t>10.128.165.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,7 +1552,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>普通资产</t>
+          <t>核心资产</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1410,7 +1573,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>未暴露</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,1061 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>数据来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSH 弱密码</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:05</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.128.165.150</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSH 弱密码</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:04</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-26 18:04</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10.128.165.151</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>businessPtwtykb_Dnanw</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>已托管</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-02 18:05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-02 18:05</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10.128.165.26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>yj设备组</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HTTP_basic弱口令漏洞</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://10.128.165.118:80</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-28 20:24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-25 20:27</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10.128.165.118</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>页面url: http://10.128.165.118:80
+请求体: GET  HTTP/1.1
+Host: 10.128.165.118:80
+User-Agent: python-requests/2.23.0
+Accept-Encoding: gzip, deflate
+Accept: */*
+Connection: keep-alive
+Authorization: Basic YWRtaW46YWRtaW4= 
+响应体: HTTP/1.1 200 OK
+Date: Tue, 19 Mar 1996 15:04:10 GMT
+Server: cisco-IOS
+Transfer-Encoding: chunked
+Content-Type: text/html
+Expires: Tue, 19 Mar 1996 15:04:10 GMT
+Last-Modified: Tue, 19 Mar 1996 15:04:10 GMT
+Cache-Control: no-store, no-cache, must-revalidate
+Accept-Ranges: none 
+ &lt;!-- Copyright (c) 2003-2006, 2008 by Cisco Systems, Inc. --&gt;
+&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.0 Transitional//EN"&gt;
+&lt;html&gt;
+&lt;head&gt;
+&lt;meta http-equiv="pragma" content="no-cache"&gt;
+&lt;LINK rel="stylesheet" href="stylesheet.css" type="text/css"&gt;
+&lt;title&gt;&lt;/title&gt;
+&lt;style&gt;
+.rightTopBorder {
+	border-top:2px inset;
+	border-right:2px inset;
+}
+.leftTopBorder {
+	border-top:2px inset;
+	border-left:2px inset;
+}
+&lt;/style&gt;
+&lt;script language="JavaScript" src="preflight.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="ajax.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="discover.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="framework.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="fpv.js"&gt;&lt;/script&gt;
+&lt;script language="JavaScript" src="title.js"&gt;&lt;/script&gt;
+&lt;script&gt;
+top.dataCache.put("LANGUAGE_CODE", "en");
+top.dataCache.put("CHARSET", "Windows-1252");
+var documentURL = document.location.href;
+var userPreference = retrieveCookie("SSLPreference");
+function initCookie(){
+	var cookie = retrieveCookie("gettingstarted");
+	if(cookie == "")
+	{
+		top.showHelp("Getting Started");
+		document.cookie = "gettingstarted=1;expires=" + cookieExpiryDate();
+	}
+}
+function retrieveCookie(_cookieName) {
+	var cookies = document.cookie.split("; ");
+	for (var i=0; i &lt; cookies.length; i++)
+	{
+	var cookieName = cookies[i].split("=");
+	if (_cookieName == cookieName[0]) 
+	  return unescape(cookieName[1]);
+	}
+	return "";
+}
+function cookieExpiryDate() {
+	date = new Date();
+	return (new Date(date.setDate(date.getYear()+10))).toGMTString();
+} 
+if(getcookie("Cisco_DeviceManager")) 
+{}
+	else
+{
+launchPreflight();
+}
+function loadHTTPS(rememberPref, securePort) {
+	var port = "";
+	if(rememberPref)
+		document.cookie = "SSLPreference=2;expires=" + top.cookieExpiryDate();
+	if(securePort != "" &amp;&amp; !isNaN(parseInt(securePort)) &amp;&amp; parseInt(securePort) != 443)
+		port = ":" + securePort;
+	//alert(documentURL.replace(/http:\/\//, "https://").replace(/([0-9]+)\//, "$1") + port);
+	//document.location.href = documentURL.replace(/http:\/\//, "https://").replace(/([0-9]+)\//, "$1") + port;
+	document.location.href = "https://" + document.location.href.split("/")[2].split(":")[0] + port;
+}
+&lt;/script&gt;
+&lt;/head&gt;	 
+&lt;SCRIPT language="JavaScript"&gt;
+      &lt;!--
+	 window.onbeforeunload=notifyBrowserClose;
+	 if(documentURL.indexOf("http://") == 0  &amp;&amp; document.referrer.indexOf("sslhome.shtml") &lt; 0  &amp;&amp; document.referrer.indexOf("redirect.htm") &lt; 0 &amp;&amp; userPreference != 1)
+	  {
+		document.write('&lt;frameset rows="0,*" cols="*" id="sslFrameset" frameborder="no" border="0" framespacing="0"&gt;');
+	  	document.write('&lt;frame src="frmwrkResource.htm" name="resourceFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+		document.write("&lt;frame src='sslhome.shtml' name='mainFrame' scrolling='NO' marginwidth='0' marginheight='0' noresize&gt;&lt;/frame&gt;");
+	  	document.write("&lt;/frameset&gt;");	
+	  }
+	  else
+	  {
+		if(!isOlderNetscape())
+		{
+			window.document.writeln('&lt;frameset rows="0,0,0,72,134,*,1,0,0,0" cols="*" framespacing="0" frameborder="no" border="0"   onload="initCookie()"&gt;');
+			document.write('&lt;frame src="frmwrkResource.htm" name="resourceFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			window.document.writeln('&lt;frame src="discover.shtml" name="discoveryFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			window.document.write(' &lt;frame src="monitordata.shtml" name="healthFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="toolbar.shtml" name="toolbarFrame" scrolling="NO" marginwidth="2" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="topbanner.htm" name="topFrame" scrolling="NO" noresize marginwidth="2" marginheight="0"&gt;');
+			document.write('&lt;frameset cols="185,*" frameborder="yes" border="10" framespacing="10"&gt;');
+			document.write('&lt;frame src="menu.shtml" name="leftFrame" target="mainFrame"&gt;');
+			document.write('&lt;frameset name="contentFrameset" rows="*,40" cols="*" framespacing="0" frameborder="no" border="0" class="leftTopBorder"&gt;');
+			document.write('&lt;frame src="dashboard.shtml" name="mainFrame" marginwidth="2" marginheight="0"&gt;'); 
+			document.write('&lt;frame src="bottombanner.htm" name="bottomFrame" marginwidth="2" marginheight="0" scrolling="NO"&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;frame src="printframe.htm" name="printFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="submitFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="reloadStatus" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;frame src="empty.htm" name="ajaxFrame" scrolling="NO" marginwidth="0" marginheight="0" noresize&gt;');
+			document.write('&lt;noframes&gt;&lt;body&gt;');
+			document.write('These pages use Frames. Please make sure that the browser fully supports Frames feature!');
+			document.write('&lt;/body&gt;&lt;/noframes&gt;');
+			document.write('&lt;/frameset&gt;');
+			document.write('&lt;/html&gt;');
+		}
+	 }
+	// --&gt;&lt;/SCRIPT&gt;
+&lt;NOSCRIPT&gt;
+&lt;body bgcolor="#F8F8F8"&gt;
+&lt;TABLE height=63 cellSpacing=0 cellPadding=0 width="100%" bgColor="#F8F8F8"
+  border=0&gt;
+    &lt;!--DWLayoutTable--&gt;
+    &lt;TR&gt; 
+      &lt;TD vAlign=top align="left" rowSpan=2&gt;&lt;IMG height=7 
+      src="/images/spacer.gif" width=7 border=0&gt; &lt;A 
+      href="http://www.cisco.com/"&gt;&lt;IMG alt="Cisco Systems" 
+      src="/images/logo.gif"  border=0&gt;&lt;/A&gt; &lt;/TD&gt;
+     &lt;/TR&gt;
+  &lt;/TABLE&gt;
+&lt;TABLE align="center" bgcolor="#F8F8F8" cellSpacing=0 cellPadding=0 width="75%" border=0&gt;
+    &lt;TBODY&gt;
+	&lt;TR&gt;
+        &lt;TD bgcolor="#F8F8F8" vAlign=bottom align=center width=772 class="contentheader_nogradient"&gt; 
+          Startup Report&lt;/FONT&gt;&lt;/B&gt;&lt;/FONT&gt;&lt;/TD&gt;
+	&lt;/TR&gt;
+    &lt;/TBODY&gt;
+&lt;/TABLE&gt;
+&lt;TABLE  borderColorDark=#ffffff width="75%" align="center" bgColor="#858A91" borderColorLight=#ffffff border="0"  cellpadding="0" cellspacing="1"&gt;
+                      &lt;!--DWLayoutTable--&gt;
+                      &lt;TBODY&gt;
+                        &lt;TR&gt; 
+                          &lt;TD width=124 height=109 vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff 
+    bgColor=#ffffff&gt; 
+ &lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;A 
+      href="en/troubleshooting_JavaScript.htm"&gt; &lt;IMG height=32 
+      src="images/fatal_error_big.gif" width=32 border=0&gt; &lt;/A&gt; &lt;/NOSCRIPT&gt; &lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD width="152" align="center" vAlign=center bgcolor="#FFFFFF"&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;JavaScript&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD width="704" align="center" vAlign="middle" bgcolor="#FFFFFF"  &gt; 
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt; 
+                            &lt;NOSCRIPT&gt;
+                            JavaScript has not been enabled.&lt;br&gt; The device manger 
+                            will not launch until JavaScript is enabled.&lt;br&gt; Click 
+                            &lt;A 
+      href="en/troubleshooting_JavaScript.htm"&gt;here&lt;/A&gt;&amp;nbsp; for&amp;nbsp; more information.&lt;FONT 
+      color=#800000&gt;&amp;nbsp;&amp;nbsp;&lt;/FONT&gt; 
+                            &lt;/NOSCRIPT&gt;
+                            &lt;/FONT&gt;&lt;/P&gt;&lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;TR&gt; 
+                          &lt;TD height=109 vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff 
+    bgColor=#ffffff&gt; 
+		&lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;IMG height=32 
+      src="images/question.gif" width=32 border=0&gt; &lt;/NOSCRIPT&gt; &lt;b&gt;&lt;font color="#012d32" size="2" face="Arial"&gt; 
+                            &lt;/font&gt;&lt;/b&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD nowrap align=left vAlign=center bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;Internet 
+                              Browser&amp;nbsp;&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD align="center" vAlign="middle"   bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt; 
+                            &lt;NOSCRIPT&gt;
+                            The Internet browser status is unknown. Click&lt;FONT 
+      color=#012d32&gt; &lt;/FONT&gt;&lt;A 
+      href="en/troubleshooting_Browser.htm"&gt;&lt;FONT 
+      color=#013741&gt;here&lt;/FONT&gt;&lt;/A&gt; for more information.&amp;nbsp; 
+                            &lt;/NOSCRIPT&gt;
+                            &lt;/FONT&gt;&lt;/P&gt;&lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;TR&gt; 
+                          &lt;TD height=109 align=left vAlign=center borderColor=#ffffff borderColorLight=#ffffff borderColorDark=#ffffff bgColor=#ffffff&gt;&lt;FONT 
+      face=Arial size=2&gt;  
+		&lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt; &lt;IMG height=32 
+      src="images/question.gif" width=32 border=0&gt; &lt;/NOSCRIPT&gt; &lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD nowrap align="center" vAlign="middle" bgColor=#ffffff&gt; 
+                            &lt;P align="center"&gt;&lt;B&gt;&lt;FONT class="homecontentbold"&gt;Operating 
+                              System&lt;/FONT&gt;&lt;/B&gt;&lt;/P&gt;&lt;/TD&gt;
+                          &lt;TD class="homecontent" align="center" vAlign="middle" bgColor=#ffffff&gt; 
+                             &lt;NOSCRIPT&gt;
+                            &lt;P align="center"&gt;&lt;FONT class="homecontent"&gt;The operating 
+                              system status is unknown. Click&lt;FONT color=#012d32&gt; 
+                              &lt;/FONT&gt;&lt;A 
+      href="en/troubleshooting_OS.htm"&gt;&lt;FONT 
+      color=#013741&gt;here&lt;/FONT&gt;&lt;/A&gt; for more information.&amp;nbsp; &lt;/FONT&gt; 
+                            &lt;/NOSCRIPT&gt;&lt;/P&gt;
+                            &lt;/TD&gt;
+                        &lt;/TR&gt;
+                        &lt;tr&gt; 
+						  &lt;TD colspan="3" align="right" valign="bottom" bgcolor="#FFFFFF"&gt; &lt;FONT 
+           class="homecontent"&gt; Copyright (c) 2003-2006, 2008 by Cisco Systems, Inc. &lt;/FONT&gt; &lt;/td&gt; 
+                        &lt;/tr&gt;   
+                      &lt;/TBODY&gt;
+                    &lt;/TABLE&gt;
+&lt;/body&gt;
+&lt;html&gt;
+&lt;/NOSCRIPT&gt;
+举证描述: 10.128.165.118资产80端口开启了HTTP auth服务，存在弱密码。用户名:admin，密码:admin</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WinRM 弱密码</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:06</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10.128.165.28</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-26 18:04</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10.128.165.100</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:04</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10.128.165.25</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:04</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.128.165.52</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RDP 弱密码</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Admin123</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-28 18:03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:04</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10.128.165.26</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>核心资产</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>未加白</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>内网</t>
         </is>
       </c>
     </row>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>businessPtwtykb_Dnanw</t>
+          <t>52937、20538、businessPtwtykb_Dnanw</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -773,7 +773,11 @@
           <t>yj设备组</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>41385、44060、自动化创建业务系统68348、risk_asset_group1764647661、businessAumozhg_Pwojg、businessOcnvwuf_Ruwex、risk_asset_group1764611669、测试业务系统组、23099、51565</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1272,7 +1276,11 @@
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>52937、20538</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1548,7 +1556,11 @@
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>20538、父组名、未归类组</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -827,7 +827,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>192.168.73.179</t>
+          <t>192.168.79.242</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>192.168.75.50</t>
+          <t>192.168.73.179</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2077,7 +2077,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>192.168.79.242</t>
+          <t>192.168.75.50</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>192.168.79.227</t>
+          <t>192.168.79.242</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>192.168.79.227</t>
+          <t>192.168.75.50</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>192.168.75.50</t>
+          <t>192.168.73.179</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>192.168.79.242</t>
+          <t>192.168.79.227</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>192.168.73.179</t>
+          <t>192.168.79.227</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>192.168.73.182</t>
+          <t>192.168.75.187</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2868,7 +2868,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>192.168.75.187</t>
+          <t>192.168.76.68</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>192.168.76.68</t>
+          <t>192.168.73.182</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3129,7 +3129,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>192.168.75.187</t>
+          <t>192.168.76.68</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3216,7 +3216,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>192.168.76.68</t>
+          <t>192.168.75.187</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3390,7 +3390,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>192.168.75.136</t>
+          <t>192.168.71.140</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>192.168.71.140</t>
+          <t>192.168.75.136</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>192.168.71.140</t>
+          <t>192.168.76.106</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>192.168.78.80</t>
+          <t>192.168.76.106</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>192.168.76.106</t>
+          <t>192.168.71.140</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>192.168.76.106</t>
+          <t>192.168.78.80</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>192.168.76.206</t>
+          <t>192.168.70.116</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4260,7 +4260,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4434,7 +4434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>192.168.70.116</t>
+          <t>192.168.76.206</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4521,7 +4521,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5043,7 +5043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>192.168.79.44</t>
+          <t>192.168.79.137</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>192.168.79.137</t>
+          <t>192.168.78.215</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5826,7 +5826,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>192.168.78.215</t>
+          <t>192.168.79.44</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>192.168.75.79</t>
+          <t>192.168.73.184</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>192.168.75.46</t>
+          <t>192.168.73.184</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6087,7 +6087,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>192.168.73.184</t>
+          <t>192.168.75.79</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>192.168.73.184</t>
+          <t>192.168.75.46</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6609,7 +6609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>192.168.72.113</t>
+          <t>192.168.72.42</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6957,7 +6957,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>192.168.72.42</t>
+          <t>192.168.72.113</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7044,7 +7044,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>192.168.70.3</t>
+          <t>192.168.73.85</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7218,7 +7218,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>192.168.70.3</t>
+          <t>192.168.77.110</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7305,7 +7305,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>192.168.73.85</t>
+          <t>192.168.70.3</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>192.168.77.110</t>
+          <t>192.168.70.3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7653,7 +7653,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7740,7 +7740,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>192.168.78.160</t>
+          <t>192.168.74.124</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>192.168.74.124</t>
+          <t>192.168.75.103</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>192.168.75.103</t>
+          <t>192.168.78.160</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8531,7 +8531,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8618,7 +8618,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8705,7 +8705,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>192.168.71.200</t>
+          <t>192.168.75.54</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8792,7 +8792,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>192.168.78.28</t>
+          <t>192.168.71.61</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>192.168.77.15</t>
+          <t>192.168.75.54</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>192.168.71.61</t>
+          <t>192.168.78.28</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>192.168.77.15</t>
+          <t>192.168.71.200</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>192.168.75.54</t>
+          <t>192.168.71.61</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9401,7 +9401,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>192.168.75.54</t>
+          <t>192.168.77.15</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>192.168.71.61</t>
+          <t>192.168.77.15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10706,7 +10706,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10793,7 +10793,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10880,7 +10880,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11758,7 +11758,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11932,7 +11932,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12019,7 +12019,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>192.168.72.30</t>
+          <t>192.168.75.222</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>192.168.75.222</t>
+          <t>192.168.72.30</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -12193,7 +12193,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>192.168.72.30</t>
+          <t>192.168.75.222</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>192.168.75.222</t>
+          <t>192.168.72.30</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12367,7 +12367,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>192.168.78.251</t>
+          <t>192.168.76.235</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>192.168.76.235</t>
+          <t>192.168.78.251</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12889,7 +12889,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>192.168.76.171</t>
+          <t>192.168.71.245</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>192.168.71.245</t>
+          <t>192.168.76.171</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -13237,7 +13237,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13324,7 +13324,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13498,7 +13498,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13759,7 +13759,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>192.168.70.247</t>
+          <t>192.168.77.11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>192.168.77.11</t>
+          <t>192.168.70.247</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -14020,7 +14020,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>192.168.77.80</t>
+          <t>192.168.75.153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>192.168.75.153</t>
+          <t>192.168.77.80</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>192.168.72.128</t>
+          <t>192.168.76.131</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>192.168.77.91</t>
+          <t>192.168.74.236</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -15151,7 +15151,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>192.168.78.110</t>
+          <t>192.168.77.91</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>192.168.75.249</t>
+          <t>192.168.74.81</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -15325,7 +15325,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>192.168.74.236</t>
+          <t>192.168.76.131</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15412,7 +15412,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>192.168.79.185</t>
+          <t>192.168.72.128</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15499,7 +15499,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>192.168.74.81</t>
+          <t>192.168.75.249</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15586,7 +15586,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>192.168.74.236</t>
+          <t>192.168.71.100</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15673,7 +15673,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>192.168.71.100</t>
+          <t>192.168.78.110</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>192.168.75.249</t>
+          <t>192.168.74.81</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>192.168.79.136</t>
+          <t>192.168.74.236</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>192.168.72.128</t>
+          <t>192.168.75.249</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -16021,7 +16021,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>192.168.78.110</t>
+          <t>192.168.72.128</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -16108,7 +16108,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>192.168.79.136</t>
+          <t>192.168.79.185</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -16195,7 +16195,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>192.168.72.98</t>
+          <t>192.168.77.91</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -16282,7 +16282,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>192.168.77.91</t>
+          <t>192.168.79.185</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>192.168.76.131</t>
+          <t>192.168.73.206</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>192.168.74.81</t>
+          <t>192.168.79.136</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>192.168.79.185</t>
+          <t>192.168.71.100</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>192.168.71.100</t>
+          <t>192.168.72.98</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -16717,7 +16717,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>192.168.76.131</t>
+          <t>192.168.78.110</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>192.168.73.206</t>
+          <t>192.168.79.136</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -16978,7 +16978,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>192.168.72.229</t>
+          <t>192.168.74.195</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -17326,7 +17326,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>192.168.74.195</t>
+          <t>192.168.72.229</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -17500,7 +17500,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17761,7 +17761,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17848,7 +17848,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17935,7 +17935,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -18022,7 +18022,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>192.168.70.81</t>
+          <t>192.168.78.76</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>192.168.72.210</t>
+          <t>192.168.73.54</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>192.168.70.81</t>
+          <t>192.168.73.123</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>192.168.75.177</t>
+          <t>192.168.73.54</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -18457,7 +18457,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>192.168.71.153</t>
+          <t>192.168.72.210</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -18544,7 +18544,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>192.168.73.123</t>
+          <t>192.168.78.76</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -18631,7 +18631,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>192.168.74.216</t>
+          <t>192.168.71.153</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -18718,7 +18718,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>192.168.72.162</t>
+          <t>192.168.70.149</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -18805,7 +18805,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>192.168.71.153</t>
+          <t>192.168.78.159</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>192.168.78.159</t>
+          <t>192.168.70.81</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -18979,7 +18979,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>192.168.74.216</t>
+          <t>192.168.75.177</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>192.168.72.162</t>
+          <t>192.168.78.159</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>192.168.75.219</t>
+          <t>192.168.76.133</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>192.168.78.76</t>
+          <t>192.168.74.216</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -19327,7 +19327,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>192.168.75.177</t>
+          <t>192.168.73.123</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>192.168.78.76</t>
+          <t>192.168.72.210</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -19501,7 +19501,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>192.168.70.149</t>
+          <t>192.168.71.153</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>192.168.75.219</t>
+          <t>192.168.70.81</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -19675,7 +19675,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>192.168.73.54</t>
+          <t>192.168.72.162</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -19762,7 +19762,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>192.168.76.133</t>
+          <t>192.168.74.216</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>192.168.73.123</t>
+          <t>192.168.75.219</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>192.168.76.133</t>
+          <t>192.168.72.162</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -20023,7 +20023,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>192.168.73.54</t>
+          <t>192.168.75.177</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>192.168.78.159</t>
+          <t>192.168.76.133</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>192.168.72.210</t>
+          <t>192.168.75.219</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -20371,7 +20371,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>192.168.72.14</t>
+          <t>192.168.74.201</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -20458,7 +20458,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>192.168.71.162</t>
+          <t>192.168.79.115</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -20545,7 +20545,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20719,7 +20719,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>192.168.74.166</t>
+          <t>192.168.75.22</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>192.168.78.36</t>
+          <t>192.168.79.14</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -20893,7 +20893,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>192.168.72.14</t>
+          <t>192.168.72.133</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>192.168.74.155</t>
+          <t>192.168.74.166</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>192.168.74.136</t>
+          <t>192.168.71.162</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>192.168.78.36</t>
+          <t>192.168.72.133</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -21241,7 +21241,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>192.168.72.133</t>
+          <t>192.168.75.15</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>192.168.71.162</t>
+          <t>192.168.78.36</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>192.168.79.115</t>
+          <t>192.168.71.162</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -21502,7 +21502,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>192.168.74.166</t>
+          <t>192.168.72.14</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>192.168.74.201</t>
+          <t>192.168.78.36</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>192.168.75.15</t>
+          <t>192.168.72.14</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -21763,7 +21763,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>192.168.75.22</t>
+          <t>192.168.74.155</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>192.168.79.14</t>
+          <t>192.168.74.155</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -21937,7 +21937,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>192.168.74.136</t>
+          <t>192.168.74.166</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>192.168.74.155</t>
+          <t>192.168.75.22</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>192.168.79.14</t>
+          <t>192.168.74.201</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>192.168.74.201</t>
+          <t>192.168.79.14</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>192.168.75.22</t>
+          <t>192.168.74.136</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>192.168.72.133</t>
+          <t>192.168.74.136</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -22459,7 +22459,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -22546,7 +22546,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -22981,7 +22981,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -23329,7 +23329,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -23416,7 +23416,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="L268" t="inlineStr"/>
@@ -23890,12 +23890,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -23981,12 +23981,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -23996,7 +23996,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="L270" t="inlineStr"/>
@@ -24007,7 +24007,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -24254,12 +24254,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="L273" t="inlineStr"/>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -24345,12 +24345,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="L274" t="inlineStr"/>
@@ -24371,7 +24371,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">

--- a/安全体检报告/风险清单/弱口令清单.xlsx
+++ b/安全体检报告/风险清单/弱口令清单.xlsx
@@ -653,7 +653,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>192.168.79.242</t>
+          <t>192.168.75.50</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>192.168.73.179</t>
+          <t>192.168.79.242</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2077,7 +2077,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>192.168.75.50</t>
+          <t>192.168.73.179</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>192.168.79.242</t>
+          <t>192.168.79.227</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>192.168.75.50</t>
+          <t>192.168.79.227</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>192.168.73.179</t>
+          <t>192.168.75.50</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>192.168.79.227</t>
+          <t>192.168.73.179</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>192.168.79.227</t>
+          <t>192.168.79.242</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>192.168.75.187</t>
+          <t>192.168.76.68</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>192.168.76.68</t>
+          <t>192.168.75.187</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>192.168.73.182</t>
+          <t>192.168.75.187</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>192.168.75.187</t>
+          <t>192.168.73.182</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>192.168.74.62</t>
+          <t>192.168.71.140</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>192.168.74.62</t>
+          <t>192.168.78.80</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3564,7 +3564,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>192.168.75.136</t>
+          <t>192.168.76.106</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>192.168.76.106</t>
+          <t>192.168.75.136</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>192.168.71.140</t>
+          <t>192.168.74.62</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>192.168.78.80</t>
+          <t>192.168.74.62</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4260,7 +4260,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4434,7 +4434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4521,7 +4521,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4782,7 +4782,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4956,7 +4956,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>192.168.75.224</t>
+          <t>192.168.74.169</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>192.168.74.169</t>
+          <t>192.168.75.224</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>192.168.79.137</t>
+          <t>192.168.79.44</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5565,7 +5565,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>192.168.79.137</t>
+          <t>192.168.78.215</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5739,7 +5739,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>192.168.78.215</t>
+          <t>192.168.79.137</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5826,7 +5826,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>192.168.79.44</t>
+          <t>192.168.79.137</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6087,7 +6087,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>192.168.75.79</t>
+          <t>192.168.75.46</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>192.168.75.46</t>
+          <t>192.168.75.79</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6435,7 +6435,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6522,7 +6522,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6609,7 +6609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>192.168.72.113</t>
+          <t>192.168.72.42</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>192.168.72.42</t>
+          <t>192.168.72.113</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7131,7 +7131,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>192.168.73.85</t>
+          <t>192.168.70.3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>192.168.77.110</t>
+          <t>192.168.70.3</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>192.168.70.3</t>
+          <t>192.168.77.110</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7392,7 +7392,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>192.168.70.3</t>
+          <t>192.168.73.85</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>192.168.73.85</t>
+          <t>192.168.77.110</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>192.168.77.110</t>
+          <t>192.168.73.85</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7653,7 +7653,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7740,7 +7740,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7918,7 +7918,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>192.168.74.124</t>
+          <t>192.168.75.103</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>192.168.75.103</t>
+          <t>192.168.74.124</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>192.168.74.124</t>
+          <t>192.168.75.103</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>192.168.75.103</t>
+          <t>192.168.74.124</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8705,7 +8705,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>192.168.71.61</t>
+          <t>192.168.71.200</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>192.168.71.200</t>
+          <t>192.168.71.61</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9053,7 +9053,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>192.168.78.28</t>
+          <t>192.168.77.15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>192.168.71.200</t>
+          <t>192.168.77.15</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9227,7 +9227,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>192.168.78.28</t>
+          <t>192.168.71.61</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>192.168.71.61</t>
+          <t>192.168.78.28</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>192.168.77.15</t>
+          <t>192.168.71.200</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9488,7 +9488,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>192.168.77.15</t>
+          <t>192.168.78.28</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>192.168.74.36</t>
+          <t>192.168.71.234</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>192.168.71.234</t>
+          <t>192.168.74.36</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10010,7 +10010,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10097,7 +10097,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10184,7 +10184,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10793,7 +10793,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10880,7 +10880,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10967,7 +10967,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11054,7 +11054,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11758,7 +11758,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11932,7 +11932,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12019,7 +12019,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>192.168.75.222</t>
+          <t>192.168.72.30</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>192.168.72.30</t>
+          <t>192.168.75.222</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -12193,7 +12193,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12367,7 +12367,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>192.168.76.235</t>
+          <t>192.168.78.251</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>192.168.78.251</t>
+          <t>192.168.76.235</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12715,7 +12715,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>192.168.76.235</t>
+          <t>192.168.78.251</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -12802,7 +12802,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>192.168.78.251</t>
+          <t>192.168.76.235</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -12889,7 +12889,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12976,7 +12976,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13063,7 +13063,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13585,7 +13585,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13672,7 +13672,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>192.168.77.11</t>
+          <t>192.168.70.247</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>192.168.70.247</t>
+          <t>192.168.77.11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -14281,7 +14281,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>192.168.77.80</t>
+          <t>192.168.75.153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -14368,7 +14368,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>192.168.75.153</t>
+          <t>192.168.77.80</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14455,7 +14455,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>192.168.77.80</t>
+          <t>192.168.75.153</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14542,7 +14542,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>192.168.75.153</t>
+          <t>192.168.77.80</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -14803,7 +14803,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14890,7 +14890,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>192.168.76.131</t>
+          <t>192.168.74.81</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -15064,7 +15064,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>192.168.74.236</t>
+          <t>192.168.71.100</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -15151,7 +15151,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>192.168.77.91</t>
+          <t>192.168.78.110</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>192.168.74.81</t>
+          <t>192.168.75.249</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>192.168.76.131</t>
+          <t>192.168.72.128</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>192.168.72.128</t>
+          <t>192.168.76.131</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>192.168.75.249</t>
+          <t>192.168.74.81</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -15586,7 +15586,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>192.168.71.100</t>
+          <t>192.168.77.91</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>192.168.78.110</t>
+          <t>192.168.76.131</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>192.168.74.81</t>
+          <t>192.168.74.236</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15847,7 +15847,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>192.168.74.236</t>
+          <t>192.168.79.136</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>192.168.75.249</t>
+          <t>192.168.79.136</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -16021,7 +16021,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>192.168.72.128</t>
+          <t>192.168.78.110</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -16108,7 +16108,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>192.168.79.185</t>
+          <t>192.168.72.98</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>192.168.77.91</t>
+          <t>192.168.73.206</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>192.168.79.185</t>
+          <t>192.168.71.100</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -16369,7 +16369,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>192.168.79.136</t>
+          <t>192.168.72.98</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>192.168.71.100</t>
+          <t>192.168.79.185</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>192.168.72.98</t>
+          <t>192.168.77.91</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -16717,7 +16717,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>192.168.73.206</t>
+          <t>192.168.72.128</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -16804,7 +16804,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>192.168.78.110</t>
+          <t>192.168.79.185</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -16891,7 +16891,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>192.168.79.136</t>
+          <t>192.168.74.236</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>192.168.72.98</t>
+          <t>192.168.75.249</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -17239,7 +17239,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>192.168.74.195</t>
+          <t>192.168.72.229</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -17413,7 +17413,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>192.168.72.229</t>
+          <t>192.168.74.195</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -17587,7 +17587,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17674,7 +17674,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>192.168.78.76</t>
+          <t>192.168.73.123</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>192.168.73.54</t>
+          <t>192.168.78.159</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>192.168.73.123</t>
+          <t>192.168.74.216</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -18370,7 +18370,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>192.168.73.54</t>
+          <t>192.168.76.133</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>192.168.72.210</t>
+          <t>192.168.75.177</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -18544,7 +18544,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>192.168.78.76</t>
+          <t>192.168.70.81</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>192.168.71.153</t>
+          <t>192.168.78.159</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -18718,7 +18718,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>192.168.70.149</t>
+          <t>192.168.71.153</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -18805,7 +18805,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>192.168.78.159</t>
+          <t>192.168.70.149</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>192.168.70.81</t>
+          <t>192.168.78.76</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>192.168.75.177</t>
+          <t>192.168.72.210</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>192.168.78.159</t>
+          <t>192.168.73.54</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>192.168.76.133</t>
+          <t>192.168.73.123</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>192.168.74.216</t>
+          <t>192.168.78.76</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -19327,7 +19327,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>192.168.73.123</t>
+          <t>192.168.73.54</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -19414,7 +19414,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>192.168.72.210</t>
+          <t>192.168.75.219</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>192.168.71.153</t>
+          <t>192.168.76.133</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>192.168.70.81</t>
+          <t>192.168.70.149</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -19675,7 +19675,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>192.168.72.162</t>
+          <t>192.168.75.177</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>192.168.74.216</t>
+          <t>192.168.72.162</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -19936,7 +19936,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>192.168.75.177</t>
+          <t>192.168.70.81</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>192.168.76.133</t>
+          <t>192.168.74.216</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -20197,7 +20197,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>192.168.75.219</t>
+          <t>192.168.72.210</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>192.168.70.149</t>
+          <t>192.168.71.153</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>192.168.74.201</t>
+          <t>192.168.71.162</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>192.168.79.115</t>
+          <t>192.168.72.133</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -20545,7 +20545,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20632,7 +20632,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>192.168.79.115</t>
+          <t>192.168.78.36</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>192.168.75.22</t>
+          <t>192.168.71.162</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -20806,7 +20806,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>192.168.79.14</t>
+          <t>192.168.74.166</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>192.168.72.133</t>
+          <t>192.168.75.22</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>192.168.74.166</t>
+          <t>192.168.79.14</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>192.168.71.162</t>
+          <t>192.168.72.133</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -21154,7 +21154,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>192.168.72.133</t>
+          <t>192.168.74.201</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>192.168.75.15</t>
+          <t>192.168.79.115</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>192.168.78.36</t>
+          <t>192.168.75.15</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>192.168.71.162</t>
+          <t>192.168.79.115</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>192.168.72.14</t>
+          <t>192.168.74.201</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -21589,7 +21589,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>192.168.78.36</t>
+          <t>192.168.74.136</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>192.168.72.14</t>
+          <t>192.168.79.14</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>192.168.74.155</t>
+          <t>192.168.74.136</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>192.168.74.155</t>
+          <t>192.168.75.22</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -22024,7 +22024,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>192.168.75.22</t>
+          <t>192.168.74.155</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>192.168.74.201</t>
+          <t>192.168.78.36</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>192.168.79.14</t>
+          <t>192.168.74.155</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>192.168.74.136</t>
+          <t>192.168.72.14</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>192.168.74.136</t>
+          <t>192.168.72.14</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -22807,7 +22807,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -22894,7 +22894,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -23155,7 +23155,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -23242,7 +23242,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -23329,7 +23329,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Redis 弱密码</t>
+          <t>SSH 弱密码</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -23416,7 +23416,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SSH 弱密码</t>
+          <t>Redis 弱密码</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="L267" t="inlineStr"/>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="L268" t="inlineStr"/>
@@ -23890,12 +23890,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -23981,12 +23981,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -24072,12 +24072,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>192.168.51.66</t>
+          <t>192.168.54.213</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>服务器</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>子组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -24098,7 +24098,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>退库资产</t>
+          <t>台账资产</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>192.168.54.174</t>
+          <t>192.168.54.68</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>父组名</t>
         </is>
       </c>
       <c r="L272" t="inlineStr"/>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>192.168.54.68</t>
+          <t>192.168.54.174</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>父组名</t>
+          <t>test1111</t>
         </is>
       </c>
       <c r="L273" t="inlineStr"/>
@@ -24345,12 +24345,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>192.168.54.213</t>
+          <t>192.168.51.66</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>服务器</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>test1111</t>
+          <t>子组名</t>
         </is>
       </c>
       <c r="L274" t="inlineStr"/>
@@ -24371,7 +24371,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>台账资产</t>
+          <t>退库资产</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
